--- a/buy-zapchasti-mercedes-e210-1996.xlsx
+++ b/buy-zapchasti-mercedes-e210-1996.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="224">
   <si>
     <t>Сводка по бу-запчастям Mercedes E200 (W210) 2.0, 1996</t>
   </si>
@@ -28,15 +28,6 @@
   </si>
   <si>
     <t>Позиций с ценой</t>
-  </si>
-  <si>
-    <t>COUNTA('Прайс'!$C$4:$C$96)</t>
-  </si>
-  <si>
-    <t>COUNTA('Дашборд'!$B$9:$B$15)</t>
-  </si>
-  <si>
-    <t>COUNT('Прайс'!$E$4:$E$96)</t>
   </si>
   <si>
     <t>По категориям</t>
@@ -1226,199 +1217,237 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="A4" s="4">
+        <f>COUNTA('Прайс'!$C$4:$C$96)</f>
+        <v>93</v>
+      </c>
+      <c r="C4" s="4">
+        <f>COUNTA('Дашборд'!$B$9:$B$15)</f>
         <v>7</v>
+      </c>
+      <c r="E4" s="4">
+        <f>COUNT('Прайс'!$E$4:$E$96)</f>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="F9" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A10)</f>
+        <v>30</v>
       </c>
       <c r="C10" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A10,'Прайс'!$E$4:$E$96)</f>
+        <v>3200</v>
       </c>
       <c r="D10" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A10,'Прайс'!$F$4:$F$96)</f>
+        <v>10586</v>
       </c>
       <c r="E10" s="9">
         <f>ROUND((C10+D10)/2,0)</f>
+        <v>6893</v>
       </c>
       <c r="F10" s="9">
         <f>D10-C10</f>
+        <v>7386</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A11)</f>
+        <v>7</v>
       </c>
       <c r="C11" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A11,'Прайс'!$E$4:$E$96)</f>
+        <v>13250</v>
       </c>
       <c r="D11" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A11,'Прайс'!$F$4:$F$96)</f>
+        <v>27130</v>
       </c>
       <c r="E11" s="9">
         <f>ROUND((C11+D11)/2,0)</f>
+        <v>20190</v>
       </c>
       <c r="F11" s="9">
         <f>D11-C11</f>
+        <v>13880</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A12)</f>
+        <v>13</v>
       </c>
       <c r="C12" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A12,'Прайс'!$E$4:$E$96)</f>
+        <v>8000</v>
       </c>
       <c r="D12" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A12,'Прайс'!$F$4:$F$96)</f>
+        <v>11439</v>
       </c>
       <c r="E12" s="9">
         <f>ROUND((C12+D12)/2,0)</f>
+        <v>9720</v>
       </c>
       <c r="F12" s="9">
         <f>D12-C12</f>
+        <v>3439</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A13)</f>
+        <v>6</v>
       </c>
       <c r="C13" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A13,'Прайс'!$E$4:$E$96)</f>
+        <v>700</v>
       </c>
       <c r="D13" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A13,'Прайс'!$F$4:$F$96)</f>
+        <v>4750</v>
       </c>
       <c r="E13" s="9">
         <f>ROUND((C13+D13)/2,0)</f>
+        <v>2725</v>
       </c>
       <c r="F13" s="9">
         <f>D13-C13</f>
+        <v>4050</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A14)</f>
+        <v>15</v>
       </c>
       <c r="C14" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A14,'Прайс'!$E$4:$E$96)</f>
+        <v>4273</v>
       </c>
       <c r="D14" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A14,'Прайс'!$F$4:$F$96)</f>
+        <v>11734</v>
       </c>
       <c r="E14" s="9">
         <f>ROUND((C14+D14)/2,0)</f>
+        <v>8004</v>
       </c>
       <c r="F14" s="9">
         <f>D14-C14</f>
+        <v>7461</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A15)</f>
+        <v>12</v>
       </c>
       <c r="C15" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A15,'Прайс'!$E$4:$E$96)</f>
+        <v>2083</v>
       </c>
       <c r="D15" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A15,'Прайс'!$F$4:$F$96)</f>
+        <v>6666</v>
       </c>
       <c r="E15" s="9">
         <f>ROUND((C15+D15)/2,0)</f>
+        <v>4375</v>
       </c>
       <c r="F15" s="9">
         <f>D15-C15</f>
+        <v>4583</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B16" s="8">
         <f>COUNTIF('Прайс'!$B$4:$B$96,A16)</f>
+        <v>10</v>
       </c>
       <c r="C16" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A16,'Прайс'!$E$4:$E$96)</f>
+        <v>4379</v>
       </c>
       <c r="D16" s="9">
         <f>AVERAGEIF('Прайс'!$B$4:$B$96,A16,'Прайс'!$F$4:$F$96)</f>
+        <v>11122</v>
       </c>
       <c r="E16" s="9">
         <f>ROUND((C16+D16)/2,0)</f>
+        <v>7751</v>
       </c>
       <c r="F16" s="9">
         <f>D16-C16</f>
+        <v>6743</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1435,7 +1464,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BF8DFE47-8BDD-463B-A2E5-F68055F04A5D}</x14:id>
+          <x14:id>{6BB63D3D-9A8E-40FA-ADAA-D91841DB2C9C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1446,7 +1475,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BF8DFE47-8BDD-463B-A2E5-F68055F04A5D}">
+          <x14:cfRule type="dataBar" id="{6BB63D3D-9A8E-40FA-ADAA-D91841DB2C9C}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -1476,7 +1505,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1488,7 +1517,7 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1500,28 +1529,28 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1529,13 +1558,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" s="9">
         <v>27000</v>
@@ -1545,9 +1574,10 @@
       </c>
       <c r="G4" s="9">
         <f>ROUND((E4+F4)/2,0)</f>
+        <v>88500</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1555,13 +1585,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E5" s="9">
         <v>1500</v>
@@ -1571,9 +1601,10 @@
       </c>
       <c r="G5" s="9">
         <f>ROUND((E5+F5)/2,0)</f>
+        <v>5250</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1581,25 +1612,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1607,13 +1638,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E7" s="9">
         <v>10000</v>
@@ -1623,9 +1654,10 @@
       </c>
       <c r="G7" s="9">
         <f>ROUND((E7+F7)/2,0)</f>
+        <v>15000</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1633,13 +1665,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E8" s="9">
         <v>3000</v>
@@ -1649,9 +1681,10 @@
       </c>
       <c r="G8" s="9">
         <f>ROUND((E8+F8)/2,0)</f>
+        <v>3750</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1659,13 +1692,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E9" s="9">
         <v>1000</v>
@@ -1675,9 +1708,10 @@
       </c>
       <c r="G9" s="9">
         <f>ROUND((E9+F9)/2,0)</f>
+        <v>2000</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1685,13 +1719,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" s="9">
         <v>800</v>
@@ -1701,9 +1735,10 @@
       </c>
       <c r="G10" s="9">
         <f>ROUND((E10+F10)/2,0)</f>
+        <v>1650</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1711,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E11" s="9">
         <v>3000</v>
@@ -1727,9 +1762,10 @@
       </c>
       <c r="G11" s="9">
         <f>ROUND((E11+F11)/2,0)</f>
+        <v>5500</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1737,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" s="9">
         <v>1500</v>
@@ -1753,9 +1789,10 @@
       </c>
       <c r="G12" s="9">
         <f>ROUND((E12+F12)/2,0)</f>
+        <v>2750</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1763,13 +1800,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E13" s="9">
         <v>800</v>
@@ -1779,9 +1816,10 @@
       </c>
       <c r="G13" s="9">
         <f>ROUND((E13+F13)/2,0)</f>
+        <v>1400</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1789,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E14" s="9">
         <v>3000</v>
@@ -1805,9 +1843,10 @@
       </c>
       <c r="G14" s="9">
         <f>ROUND((E14+F14)/2,0)</f>
+        <v>4500</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1815,13 +1854,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E15" s="9">
         <v>200</v>
@@ -1831,9 +1870,10 @@
       </c>
       <c r="G15" s="9">
         <f>ROUND((E15+F15)/2,0)</f>
+        <v>850</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1841,13 +1881,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E16" s="9">
         <v>3500</v>
@@ -1857,9 +1897,10 @@
       </c>
       <c r="G16" s="9">
         <f>ROUND((E16+F16)/2,0)</f>
+        <v>5250</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1867,13 +1908,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17" s="9">
         <v>2500</v>
@@ -1883,9 +1924,10 @@
       </c>
       <c r="G17" s="9">
         <f>ROUND((E17+F17)/2,0)</f>
+        <v>3750</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1893,13 +1935,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="9">
         <v>1000</v>
@@ -1909,9 +1951,10 @@
       </c>
       <c r="G18" s="9">
         <f>ROUND((E18+F18)/2,0)</f>
+        <v>2000</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1919,13 +1962,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E19" s="9">
         <v>500</v>
@@ -1935,9 +1978,10 @@
       </c>
       <c r="G19" s="9">
         <f>ROUND((E19+F19)/2,0)</f>
+        <v>1000</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1945,13 +1989,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E20" s="9">
         <v>2000</v>
@@ -1961,9 +2005,10 @@
       </c>
       <c r="G20" s="9">
         <f>ROUND((E20+F20)/2,0)</f>
+        <v>3000</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1971,13 +2016,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E21" s="9">
         <v>2000</v>
@@ -1987,9 +2032,10 @@
       </c>
       <c r="G21" s="9">
         <f>ROUND((E21+F21)/2,0)</f>
+        <v>3500</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1997,13 +2043,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E22" s="9">
         <v>500</v>
@@ -2013,9 +2059,10 @@
       </c>
       <c r="G22" s="9">
         <f>ROUND((E22+F22)/2,0)</f>
+        <v>1250</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2023,13 +2070,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E23" s="9">
         <v>1000</v>
@@ -2039,9 +2086,10 @@
       </c>
       <c r="G23" s="9">
         <f>ROUND((E23+F23)/2,0)</f>
+        <v>1000</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2049,13 +2097,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E24" s="9">
         <v>3000</v>
@@ -2065,9 +2113,10 @@
       </c>
       <c r="G24" s="9">
         <f>ROUND((E24+F24)/2,0)</f>
+        <v>4000</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2075,13 +2124,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E25" s="9">
         <v>1500</v>
@@ -2091,9 +2140,10 @@
       </c>
       <c r="G25" s="9">
         <f>ROUND((E25+F25)/2,0)</f>
+        <v>2250</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2101,13 +2151,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E26" s="9">
         <v>3000</v>
@@ -2117,9 +2167,10 @@
       </c>
       <c r="G26" s="9">
         <f>ROUND((E26+F26)/2,0)</f>
+        <v>5500</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2127,13 +2178,13 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E27" s="9">
         <v>2000</v>
@@ -2143,9 +2194,10 @@
       </c>
       <c r="G27" s="9">
         <f>ROUND((E27+F27)/2,0)</f>
+        <v>3500</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2153,13 +2205,13 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E28" s="9">
         <v>4000</v>
@@ -2169,9 +2221,10 @@
       </c>
       <c r="G28" s="9">
         <f>ROUND((E28+F28)/2,0)</f>
+        <v>6000</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2179,13 +2232,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E29" s="9">
         <v>3000</v>
@@ -2195,9 +2248,10 @@
       </c>
       <c r="G29" s="9">
         <f>ROUND((E29+F29)/2,0)</f>
+        <v>6500</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2205,13 +2259,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E30" s="9">
         <v>5000</v>
@@ -2221,9 +2275,10 @@
       </c>
       <c r="G30" s="9">
         <f>ROUND((E30+F30)/2,0)</f>
+        <v>10000</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2231,13 +2286,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E31" s="9">
         <v>2000</v>
@@ -2247,9 +2302,10 @@
       </c>
       <c r="G31" s="9">
         <f>ROUND((E31+F31)/2,0)</f>
+        <v>3500</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2257,13 +2313,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E32" s="9">
         <v>2500</v>
@@ -2273,9 +2329,10 @@
       </c>
       <c r="G32" s="9">
         <f>ROUND((E32+F32)/2,0)</f>
+        <v>3750</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2283,13 +2340,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E33" s="9">
         <v>2000</v>
@@ -2299,9 +2356,10 @@
       </c>
       <c r="G33" s="9">
         <f>ROUND((E33+F33)/2,0)</f>
+        <v>3000</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2309,13 +2367,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E34" s="9">
         <v>10000</v>
@@ -2325,9 +2383,10 @@
       </c>
       <c r="G34" s="9">
         <f>ROUND((E34+F34)/2,0)</f>
+        <v>33860</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2335,13 +2394,13 @@
         <v>32</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E35" s="9">
         <v>35000</v>
@@ -2351,9 +2410,10 @@
       </c>
       <c r="G35" s="9">
         <f>ROUND((E35+F35)/2,0)</f>
+        <v>35000</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2361,25 +2421,25 @@
         <v>33</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2387,13 +2447,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E37" s="9">
         <v>1700</v>
@@ -2403,9 +2463,10 @@
       </c>
       <c r="G37" s="9">
         <f>ROUND((E37+F37)/2,0)</f>
+        <v>4450</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2413,25 +2474,25 @@
         <v>35</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2439,25 +2500,25 @@
         <v>36</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2465,13 +2526,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E40" s="9">
         <v>6300</v>
@@ -2481,9 +2542,10 @@
       </c>
       <c r="G40" s="9">
         <f>ROUND((E40+F40)/2,0)</f>
+        <v>7450</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2491,13 +2553,13 @@
         <v>38</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E41" s="9">
         <v>3000</v>
@@ -2507,9 +2569,10 @@
       </c>
       <c r="G41" s="9">
         <f>ROUND((E41+F41)/2,0)</f>
+        <v>3450</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2517,25 +2580,25 @@
         <v>39</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2543,25 +2606,25 @@
         <v>40</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2569,13 +2632,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E44" s="9">
         <v>3000</v>
@@ -2585,9 +2648,10 @@
       </c>
       <c r="G44" s="9">
         <f>ROUND((E44+F44)/2,0)</f>
+        <v>3708</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2595,25 +2659,25 @@
         <v>42</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2621,25 +2685,25 @@
         <v>43</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2647,25 +2711,25 @@
         <v>44</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2673,25 +2737,25 @@
         <v>45</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2699,13 +2763,13 @@
         <v>46</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E49" s="9">
         <v>18000</v>
@@ -2715,9 +2779,10 @@
       </c>
       <c r="G49" s="9">
         <f>ROUND((E49+F49)/2,0)</f>
+        <v>22000</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2725,25 +2790,25 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2751,25 +2816,25 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2777,25 +2842,25 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2803,25 +2868,25 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2829,13 +2894,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E54" s="9">
         <v>700</v>
@@ -2845,9 +2910,10 @@
       </c>
       <c r="G54" s="9">
         <f>ROUND((E54+F54)/2,0)</f>
+        <v>2600</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2855,25 +2921,25 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2881,25 +2947,25 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H56" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2907,25 +2973,25 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2933,25 +2999,25 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2959,13 +3025,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E59" s="9">
         <v>700</v>
@@ -2975,9 +3041,10 @@
       </c>
       <c r="G59" s="9">
         <f>ROUND((E59+F59)/2,0)</f>
+        <v>2850</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2985,13 +3052,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E60" s="9">
         <v>3500</v>
@@ -3001,9 +3068,10 @@
       </c>
       <c r="G60" s="9">
         <f>ROUND((E60+F60)/2,0)</f>
+        <v>9250</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3011,13 +3079,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E61" s="9">
         <v>10000</v>
@@ -3027,9 +3095,10 @@
       </c>
       <c r="G61" s="9">
         <f>ROUND((E61+F61)/2,0)</f>
+        <v>17500</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3037,13 +3106,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E62" s="9">
         <v>2500</v>
@@ -3053,9 +3122,10 @@
       </c>
       <c r="G62" s="9">
         <f>ROUND((E62+F62)/2,0)</f>
+        <v>4500</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3063,13 +3133,13 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E63" s="9">
         <v>5000</v>
@@ -3079,9 +3149,10 @@
       </c>
       <c r="G63" s="9">
         <f>ROUND((E63+F63)/2,0)</f>
+        <v>10000</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3089,13 +3160,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E64" s="9">
         <v>3000</v>
@@ -3105,9 +3176,10 @@
       </c>
       <c r="G64" s="9">
         <f>ROUND((E64+F64)/2,0)</f>
+        <v>5875</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3115,13 +3187,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E65" s="9">
         <v>3000</v>
@@ -3131,9 +3203,10 @@
       </c>
       <c r="G65" s="9">
         <f>ROUND((E65+F65)/2,0)</f>
+        <v>8822</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3141,13 +3214,13 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E66" s="9">
         <v>5000</v>
@@ -3157,9 +3230,10 @@
       </c>
       <c r="G66" s="9">
         <f>ROUND((E66+F66)/2,0)</f>
+        <v>8500</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3167,13 +3241,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E67" s="9">
         <v>10000</v>
@@ -3183,9 +3257,10 @@
       </c>
       <c r="G67" s="9">
         <f>ROUND((E67+F67)/2,0)</f>
+        <v>17500</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3193,13 +3268,13 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E68" s="9">
         <v>8000</v>
@@ -3209,9 +3284,10 @@
       </c>
       <c r="G68" s="9">
         <f>ROUND((E68+F68)/2,0)</f>
+        <v>10778</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3219,13 +3295,13 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E69" s="9">
         <v>3000</v>
@@ -3235,9 +3311,10 @@
       </c>
       <c r="G69" s="9">
         <f>ROUND((E69+F69)/2,0)</f>
+        <v>5500</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3245,13 +3322,13 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E70" s="9">
         <v>2090</v>
@@ -3261,9 +3338,10 @@
       </c>
       <c r="G70" s="9">
         <f>ROUND((E70+F70)/2,0)</f>
+        <v>3545</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3271,13 +3349,13 @@
         <v>68</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E71" s="9">
         <v>1500</v>
@@ -3287,9 +3365,10 @@
       </c>
       <c r="G71" s="9">
         <f>ROUND((E71+F71)/2,0)</f>
+        <v>3250</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3297,13 +3376,13 @@
         <v>69</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E72" s="9">
         <v>5000</v>
@@ -3313,9 +3392,10 @@
       </c>
       <c r="G72" s="9">
         <f>ROUND((E72+F72)/2,0)</f>
+        <v>9278</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3323,13 +3403,13 @@
         <v>70</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E73" s="9">
         <v>1500</v>
@@ -3339,9 +3419,10 @@
       </c>
       <c r="G73" s="9">
         <f>ROUND((E73+F73)/2,0)</f>
+        <v>3250</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3349,13 +3430,13 @@
         <v>71</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E74" s="9">
         <v>1000</v>
@@ -3365,9 +3446,10 @@
       </c>
       <c r="G74" s="9">
         <f>ROUND((E74+F74)/2,0)</f>
+        <v>2500</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3375,13 +3457,13 @@
         <v>72</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E75" s="9">
         <v>4000</v>
@@ -3391,9 +3473,10 @@
       </c>
       <c r="G75" s="9">
         <f>ROUND((E75+F75)/2,0)</f>
+        <v>7000</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3401,13 +3484,13 @@
         <v>73</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E76" s="9">
         <v>3000</v>
@@ -3417,9 +3500,10 @@
       </c>
       <c r="G76" s="9">
         <f>ROUND((E76+F76)/2,0)</f>
+        <v>7500</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3427,13 +3511,13 @@
         <v>74</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E77" s="9">
         <v>2000</v>
@@ -3443,9 +3527,10 @@
       </c>
       <c r="G77" s="9">
         <f>ROUND((E77+F77)/2,0)</f>
+        <v>4500</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3453,13 +3538,13 @@
         <v>75</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E78" s="9">
         <v>1000</v>
@@ -3469,9 +3554,10 @@
       </c>
       <c r="G78" s="9">
         <f>ROUND((E78+F78)/2,0)</f>
+        <v>2000</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3479,13 +3565,13 @@
         <v>76</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E79" s="9">
         <v>1500</v>
@@ -3495,9 +3581,10 @@
       </c>
       <c r="G79" s="9">
         <f>ROUND((E79+F79)/2,0)</f>
+        <v>3750</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3505,13 +3592,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E80" s="9">
         <v>2000</v>
@@ -3521,9 +3608,10 @@
       </c>
       <c r="G80" s="9">
         <f>ROUND((E80+F80)/2,0)</f>
+        <v>3933</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3531,13 +3619,13 @@
         <v>78</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E81" s="9">
         <v>1500</v>
@@ -3547,9 +3635,10 @@
       </c>
       <c r="G81" s="9">
         <f>ROUND((E81+F81)/2,0)</f>
+        <v>2750</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3557,13 +3646,13 @@
         <v>79</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E82" s="9">
         <v>1500</v>
@@ -3573,9 +3662,10 @@
       </c>
       <c r="G82" s="9">
         <f>ROUND((E82+F82)/2,0)</f>
+        <v>3250</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3583,13 +3673,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E83" s="9">
         <v>500</v>
@@ -3599,9 +3689,10 @@
       </c>
       <c r="G83" s="9">
         <f>ROUND((E83+F83)/2,0)</f>
+        <v>1000</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3609,13 +3700,13 @@
         <v>81</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E84" s="9">
         <v>3000</v>
@@ -3625,9 +3716,10 @@
       </c>
       <c r="G84" s="9">
         <f>ROUND((E84+F84)/2,0)</f>
+        <v>4313</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3635,13 +3727,13 @@
         <v>82</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E85" s="9">
         <v>3000</v>
@@ -3651,9 +3743,10 @@
       </c>
       <c r="G85" s="9">
         <f>ROUND((E85+F85)/2,0)</f>
+        <v>9000</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3661,13 +3754,13 @@
         <v>83</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E86" s="9">
         <v>2000</v>
@@ -3677,9 +3770,10 @@
       </c>
       <c r="G86" s="9">
         <f>ROUND((E86+F86)/2,0)</f>
+        <v>3500</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3687,13 +3781,13 @@
         <v>84</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E87" s="9">
         <v>8000</v>
@@ -3703,9 +3797,10 @@
       </c>
       <c r="G87" s="9">
         <f>ROUND((E87+F87)/2,0)</f>
+        <v>10000</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3713,13 +3808,13 @@
         <v>85</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E88" s="9">
         <v>15000</v>
@@ -3729,9 +3824,10 @@
       </c>
       <c r="G88" s="9">
         <f>ROUND((E88+F88)/2,0)</f>
+        <v>20000</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3739,13 +3835,13 @@
         <v>86</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E89" s="9">
         <v>4000</v>
@@ -3755,9 +3851,10 @@
       </c>
       <c r="G89" s="9">
         <f>ROUND((E89+F89)/2,0)</f>
+        <v>9500</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3765,13 +3862,13 @@
         <v>87</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E90" s="9">
         <v>1785</v>
@@ -3781,9 +3878,10 @@
       </c>
       <c r="G90" s="9">
         <f>ROUND((E90+F90)/2,0)</f>
+        <v>3893</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3791,13 +3889,13 @@
         <v>88</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E91" s="9">
         <v>3000</v>
@@ -3807,9 +3905,10 @@
       </c>
       <c r="G91" s="9">
         <f>ROUND((E91+F91)/2,0)</f>
+        <v>9608</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3817,13 +3916,13 @@
         <v>89</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E92" s="9">
         <v>3000</v>
@@ -3833,9 +3932,10 @@
       </c>
       <c r="G92" s="9">
         <f>ROUND((E92+F92)/2,0)</f>
+        <v>6500</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3843,13 +3943,13 @@
         <v>90</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E93" s="9">
         <v>3000</v>
@@ -3859,9 +3959,10 @@
       </c>
       <c r="G93" s="9">
         <f>ROUND((E93+F93)/2,0)</f>
+        <v>7500</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3869,13 +3970,13 @@
         <v>91</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E94" s="9">
         <v>1500</v>
@@ -3885,9 +3986,10 @@
       </c>
       <c r="G94" s="9">
         <f>ROUND((E94+F94)/2,0)</f>
+        <v>2750</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3895,13 +3997,13 @@
         <v>92</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E95" s="9">
         <v>3000</v>
@@ -3911,9 +4013,10 @@
       </c>
       <c r="G95" s="9">
         <f>ROUND((E95+F95)/2,0)</f>
+        <v>5500</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3921,13 +4024,13 @@
         <v>93</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E96" s="9">
         <v>1500</v>
@@ -3937,9 +4040,10 @@
       </c>
       <c r="G96" s="9">
         <f>ROUND((E96+F96)/2,0)</f>
+        <v>2250</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3966,7 +4070,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3974,7 +4078,7 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3982,142 +4086,142 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>194</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>212</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/buy-zapchasti-mercedes-e210-1996.xlsx
+++ b/buy-zapchasti-mercedes-e210-1996.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="Дашборд" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Прайс" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Источники" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="О прайсе" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="232">
   <si>
     <t>Сводка по бу-запчастям Mercedes E200 (W210) 2.0, 1996</t>
   </si>
@@ -685,6 +686,30 @@
   </si>
   <si>
     <t>~57,7 тыс. руб под заказ</t>
+  </si>
+  <si>
+    <t>ExcelPrice — цены на любые запчасти</t>
+  </si>
+  <si>
+    <t>Полные прайс-листы по моделям авто: все запчасти + актуальные цены со всего интернета</t>
+  </si>
+  <si>
+    <t>Заказать свой прайс: https://excelprice.ru</t>
+  </si>
+  <si>
+    <t>Контакты:</t>
+  </si>
+  <si>
+    <t>Telegram: @Excelprice</t>
+  </si>
+  <si>
+    <t>WhatsApp: +7 (900) 000-44-69</t>
+  </si>
+  <si>
+    <t>Email: dot.akc@yandex.ru</t>
+  </si>
+  <si>
+    <t>Если этот файл вам прислали — вы можете заказать такой же прайс на свою модель на сайте excelprice.ru</t>
   </si>
 </sst>
 </file>
@@ -695,7 +720,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;[Red]-#,##0&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -739,6 +764,35 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF667085"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF2F5597"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667085"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="13"/>
+      <color rgb="FF2A7F77"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2A37"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
       <sz val="10"/>
       <color rgb="FF667085"/>
       <name val="Calibri"/>
@@ -799,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -836,6 +890,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1470,22 +1529,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6BB63D3D-9A8E-40FA-ADAA-D91841DB2C9C}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E10:E16</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4053,7 +4097,7 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4230,6 +4274,66 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="A7" r:id="rId2"/>
+    <hyperlink ref="A8" r:id="rId3"/>
+    <hyperlink ref="A9" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>